--- a/Ärisõnastik.xlsx
+++ b/Ärisõnastik.xlsx
@@ -8,89 +8,97 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sipsik\Documents\Koolituste-kasumlikkuse-m-jutegurid\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1EE15E85-9340-4894-9CF4-E9A31ADCA7CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBE8FF95-F13B-4F5B-AF47-BC202A72D595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21660" yWindow="2040" windowWidth="17280" windowHeight="8880" xr2:uid="{E7751FDA-1F83-4417-BB18-0B0AC84F78A7}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9979DDDE-42EA-4405-B76E-E54E69F71E5C}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Ärisõnastik" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
-  <si>
-    <t>Müügitulu ak/h kohta</t>
-  </si>
-  <si>
-    <t>Mõõdik, mis näitab, kui palju tulu toob üks lektori töötund (sh ettevalmistus).</t>
-  </si>
-  <si>
-    <t>Kobarkoolitus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lektori AK/h müügitulu </t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+  <si>
+    <t>Mõiste</t>
+  </si>
+  <si>
+    <t>Selgitus</t>
+  </si>
+  <si>
+    <t>Müügitulu AK/h kohta</t>
+  </si>
+  <si>
+    <t>Koolituste müügitulu jagatud koolituste akadeemiliste tundide arvuga.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Koolitaja AK/h müügitulu </t>
+  </si>
+  <si>
+    <t>Koolituse müügitulu jagatud koolitaja logitud töötundidega</t>
+  </si>
+  <si>
+    <t>Madalhooaeg</t>
+  </si>
+  <si>
+    <t>Periood jaanuar, mai-juuli</t>
+  </si>
+  <si>
+    <t>Kõrghooaeg</t>
+  </si>
+  <si>
+    <t>Periood august-detsember, veebruar-aprill</t>
   </si>
   <si>
     <t>Koolitus</t>
   </si>
   <si>
+    <t xml:space="preserve">Õppesündmus või kursus, millel on konkreetne teema, toimumisaeg ja määratud lektor. </t>
+  </si>
+  <si>
     <t>Allahindlus</t>
   </si>
   <si>
-    <t xml:space="preserve"> Koolitustüüp, mis koosneb mitmest moodulist (väli KasKobarkoolitus -True).</t>
-  </si>
-  <si>
-    <t>Arvutuslik väärtus: koolituse kogukäive jagatud akadeemiliste tundide arvuga.</t>
-  </si>
-  <si>
-    <t>Madalhooaeg</t>
-  </si>
-  <si>
-    <t>Periood mai -august</t>
-  </si>
-  <si>
-    <t>Kõrghooaeg</t>
-  </si>
-  <si>
-    <t>Periood september - aprill</t>
-  </si>
-  <si>
-    <t>Ühekordne õppesündmus või kursus, millel on konkreetne teema, toimumisaeg ja määratud lektor. Ärilises vaates on see peamine tulu genereeriv üksus.</t>
-  </si>
-  <si>
-    <t>Mahukam koolitusprojekt, mis koosneb mitmest moodulist või korduvast koolitusest.</t>
-  </si>
-  <si>
-    <t>Arvutuslik vahe standardse osalustasu ja tegelikult realiseerunud müügitulu vahel.</t>
+    <t>Väärtus protsentides, algselt määratud kohamaksumuse ja tegelikult realiseerunud müügitulu suhe.</t>
+  </si>
+  <si>
+    <t>Koolitaja</t>
+  </si>
+  <si>
+    <t>Inimene, kes viib läbi koolitust.</t>
+  </si>
+  <si>
+    <t>Töö kategooria</t>
+  </si>
+  <si>
+    <t>Koolitaja töötundide jagunemine: koolitustunnid ehk koolituse läbiviimiselele kulunud tunnid, töötunnid ehk ettevalmistusaeg.</t>
+  </si>
+  <si>
+    <t>Koolituse kategooria</t>
+  </si>
+  <si>
+    <t>Koolituste jagunemist iseloomustav lühend (SPE, KAS, PRO, DEV jne)</t>
+  </si>
+  <si>
+    <t>Koolitaja kategooria</t>
+  </si>
+  <si>
+    <t>Oma koolitaja (koolitusettevõtte põhikohaga töötaja) või külaliskoolitaja(lepinguline partner)</t>
+  </si>
+  <si>
+    <t>Koolitustundide osakaal</t>
+  </si>
+  <si>
+    <t>Koolitustundide osakaal kogu tundidest (ettevalmistus + koolitus)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -100,7 +108,134 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="186"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <charset val="186"/>
+      <scheme val="major"/>
+    </font>
+    <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="186"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="186"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="186"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="186"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="186"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="186"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="186"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="186"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="186"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="186"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="186"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="186"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="186"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -109,23 +244,209 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="186"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -133,20 +454,221 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="42">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -477,80 +999,109 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9331D44A-FB5F-49CE-B472-5BA5964A583D}">
-  <dimension ref="A1:B9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A77CB742-2B15-4798-A200-08ECF5A388CA}">
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="86.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.6640625" customWidth="1"/>
+    <col min="2" max="2" width="109.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>7</v>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
+      <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
+      <c r="A8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
+      <c r="A9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
